--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
@@ -5308,7 +5308,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
@@ -5308,7 +5308,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20261003_223546.xlsx
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
